--- a/basedatos_partidas/salida/descompuestos/12.04.01.190.xlsx
+++ b/basedatos_partidas/salida/descompuestos/12.04.01.190.xlsx
@@ -593,7 +593,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-SOPORTE-AC</t>
+          <t>MT-PERNO-ANCLA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Soporte metálico galvanizado para unidad condensadora, con sus anclajes.</t>
+          <t>Perno de anclaje de acero con tuerca y arandela, para fijación de placa base.</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>83.09</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="14">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>86.69</v>
+        <v>59.09</v>
       </c>
       <c r="H22" t="n">
-        <v>0.87</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="23">
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>87.56</v>
+        <v>59.68</v>
       </c>
     </row>
   </sheetData>
